--- a/data/trending_integrated_20261012_14.xlsx
+++ b/data/trending_integrated_20261012_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19953446620</v>
+        <v>19956968580</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,10 +670,10 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>113</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132052458080</v>
+        <v>132091867280</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13650</v>
+        <v>13770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.53%</t>
+          <t>'+23.61%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>173989035135</v>
+        <v>175084873275</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1590</v>
+        <v>1602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.64%</t>
+          <t>'+15.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11316661800</v>
+        <v>11385854768</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7660</v>
+        <v>7590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+7.20%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>118080958555</v>
+        <v>119333863350</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14460</v>
+        <v>14420</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F7" t="n">
         <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>149623367000</v>
+        <v>150093964065</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>조막손 언급과 함께 개미 꼬신다는 부정적 인식. 주가 변동성에 대한 불만 및 보유 가능성에 대한 의문 제기.</t>
+          <t>미국 방산주 상승에 따른 테마 기대감. 보호예수 해제 및 매물 출회 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['개미', '변동성', '주가']</t>
+          <t>['방산', '테마', '보호예수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3780</v>
+        <v>3795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.20%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>70647556068</v>
+        <v>71299216754</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44900</v>
+        <v>45150</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.64%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="F9" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G9" t="n">
-        <v>2761</v>
+        <v>2782</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>36102653575</v>
+        <v>36729559925</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 1차 치료제 리보세라닙·캄렐리주맙 병용요법 FDA 재승인 서류 제출 공시. 연말 30만 기대감 및 공매도 관련 논의.</t>
+          <t>FDA 재승인 서류 제출에 따른 기대감 고조. 공매도 세력에 대한 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '공시', '간암']</t>
+          <t>['FDA', '재승인', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2250</v>
+        <v>2255</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.17%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H10" t="n">
         <v>1.48</v>
@@ -1346,7 +1346,7 @@
         <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>30782728446</v>
+        <v>30920050106</v>
       </c>
       <c r="P10" t="n">
         <v>2465</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1630000</v>
+        <v>16140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>510</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>1945</v>
+        <v>771</v>
       </c>
       <c r="H11" t="n">
-        <v>49.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1681000</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>1640000</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>1653000</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>1605000</v>
+        <v>16050</v>
       </c>
       <c r="N11" t="n">
-        <v>49.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>3384907302500</v>
+        <v>54847279400</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-244000</v>
+        <v>544000</v>
       </c>
       <c r="S11" t="n">
-        <v>13000</v>
+        <v>-97000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 요인(이재명 정부)과 증시 하락 연관성에 대한 강한 부정적 언급. 주가 폭락 및 주주 버려진 듯한 심경 토로.</t>
+          <t>대차 거래 및 공매도에 대한 의혹 제기. 주가 하락 요인으로 지목하며 반발.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '주가', '하락']</t>
+          <t>['대차', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,191 +1476,191 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10990</v>
+        <v>1626000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.09%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>514</v>
       </c>
       <c r="G12" t="n">
-        <v>94</v>
+        <v>1930</v>
       </c>
       <c r="H12" t="n">
-        <v>0.41</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11340</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>11340</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>12470</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>10810</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.44</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>29770909180</v>
+        <v>3481399299500</v>
       </c>
       <c r="P12" t="n">
-        <v>29750</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>10810</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>8000</v>
+        <v>-244000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>정치적 요인 및 경영진의 결정에 따른 주가 하락에 대한 불만. 투자자 이탈 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['정치', '경영', '주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16140</v>
+        <v>10940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>738</v>
+        <v>103</v>
       </c>
       <c r="H13" t="n">
-        <v>9.470000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16670</v>
+        <v>11340</v>
       </c>
       <c r="K13" t="n">
-        <v>16500</v>
+        <v>11340</v>
       </c>
       <c r="L13" t="n">
-        <v>16870</v>
+        <v>12470</v>
       </c>
       <c r="M13" t="n">
-        <v>16050</v>
+        <v>10810</v>
       </c>
       <c r="N13" t="n">
-        <v>9.460000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>53594010305</v>
+        <v>29843283860</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>29750</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>10810</v>
       </c>
       <c r="R13" t="n">
-        <v>544000</v>
+        <v>8000</v>
       </c>
       <c r="S13" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차 해지와 관련한 의혹 제기 및 뱅크런 언급. 주가 하락에 대한 불만과 범죄 행위 언급.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '주가 하락']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252750</v>
+        <v>252250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="G14" t="n">
-        <v>1905</v>
+        <v>2019</v>
       </c>
       <c r="H14" t="n">
         <v>46.35</v>
@@ -1708,13 +1708,13 @@
         <v>262500</v>
       </c>
       <c r="M14" t="n">
-        <v>252000</v>
+        <v>251500</v>
       </c>
       <c r="N14" t="n">
         <v>46.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2959347654000</v>
+        <v>3086090316250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>총선 이후 여당에 대한 부정적 언급과 함께 주가 하락의 원인을 정치적 요인으로 지목. 외인 및 기관 이탈에 대한 우려 제기.</t>
+          <t>정치적 논란으로 인한 주가 하락에 대한 불만 토로. 외인 및 기관 이탈 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '하락', '외인']</t>
+          <t>['정치', '이탈', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18170</v>
+        <v>18140</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H15" t="n">
         <v>27.61</v>
@@ -1806,7 +1806,7 @@
         <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>42631240965</v>
+        <v>43734576765</v>
       </c>
       <c r="P15" t="n">
         <v>35350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 신저가 기록. 실적 대비 주가 부진에 대한 불만.</t>
+          <t>실적 호조에도 불구하고 주가 하락, 공매도 증가에 대한 불만. 조선주 순환매 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '실적', '주가']</t>
+          <t>['실적', '공매도', '순환매']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7790</v>
+        <v>7810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.53%</t>
+          <t>'-4.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>25738035610</v>
+        <v>27239343940</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기업 가치 저평가 및 재무 악화 우려, 유상증자 가능성 제기.</t>
+          <t>기업 가치 저평가 및 실적 악화에 대한 불안감 표출. 유상증자 및 상폐 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['기업 가치', '유상증자']</t>
+          <t>['기업가치', '유상증자', '실적']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15930</v>
+        <v>15960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.13%</t>
+          <t>'-5.95%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G17" t="n">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>76455978940</v>
+        <v>77006593610</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26050</v>
+        <v>26000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
         <v>107</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>56633695100</v>
+        <v>57761104525</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3855</v>
+        <v>3845</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-9.72%</t>
+          <t>'-9.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>18419133099</v>
+        <v>18481797539</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_14.xlsx
+++ b/data/trending_integrated_20261012_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19956968580</v>
+        <v>19964303180</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132091867280</v>
+        <v>132103845020</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13770</v>
+        <v>13730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.61%</t>
+          <t>'+23.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>175084873275</v>
+        <v>176341980630</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -803,14 +803,14 @@
         <v>3200</v>
       </c>
       <c r="R4" t="n">
-        <v>-446000</v>
+        <v>-442000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인 대량 매도 확인, 금호전기 상장 영향 가능성 언급.</t>
+          <t>금호건설 주가 상승 기대감 속 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외인 매도', '금호전기']</t>
+          <t>['주가 상승', '외인 매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.50%</t>
+          <t>'+15.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11385854768</v>
+        <v>11431505728</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -895,7 +895,7 @@
         <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>-392000</v>
+        <v>-385000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7590</v>
+        <v>7580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.20%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F6" t="n">
         <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>119333863350</v>
+        <v>120469328175</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -987,23 +987,23 @@
         <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>-79000</v>
+        <v>-54000</v>
       </c>
       <c r="S6" t="n">
         <v>246000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>성수메가프로젝트, 건설기초소재 관련 긍정적 언급과 함께 공매도 관련 논의. 레미콘 부지 재개발 확정 기대감.</t>
+          <t>삼표시멘트 건설 기초 소재 사업 성장 기대 및 투신 매수세 유입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설', '공매도', '재개발']</t>
+          <t>['건설 기초 소재', '투신 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14420</v>
+        <v>14080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.67%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G7" t="n">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>150093964065</v>
+        <v>153679679195</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 방산주 상승에 따른 테마 기대감. 보호예수 해제 및 매물 출회 우려.</t>
+          <t>덕산넵코어스 주가 변동성 심화 및 투자 심리 위축, 매도 압력 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['방산', '테마', '보호예수']</t>
+          <t>['주가 변동성', '매도 압력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3795</v>
+        <v>3735</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
         <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>71299216754</v>
+        <v>71937409953</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1171,10 +1171,10 @@
         <v>2200</v>
       </c>
       <c r="R8" t="n">
-        <v>60000</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="n">
-        <v>-79000</v>
+        <v>-82000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45150</v>
+        <v>44950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-1.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F9" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G9" t="n">
-        <v>2782</v>
+        <v>2827</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>36729559925</v>
+        <v>37254598675</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1263,23 +1263,23 @@
         <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-112000</v>
+        <v>-153000</v>
       </c>
       <c r="S9" t="n">
         <v>1000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 재승인 서류 제출에 따른 기대감 고조. 공매도 세력에 대한 비판.</t>
+          <t>HLB 간암 치료제 FDA 재승인 서류 제출 완료, 상한가 기대감 고조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '재승인', '공매도']</t>
+          <t>['FDA 재승인', '리보세라닙', '공시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2255</v>
+        <v>2260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.17%</t>
+          <t>'-1.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>30920050106</v>
+        <v>31743824559</v>
       </c>
       <c r="P10" t="n">
         <v>2465</v>
@@ -1355,7 +1355,7 @@
         <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-498000</v>
+        <v>-497000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16140</v>
+        <v>16090</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="H11" t="n">
         <v>9.470000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>54847279400</v>
+        <v>55828522425</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1447,10 +1447,10 @@
         <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>544000</v>
+        <v>624000</v>
       </c>
       <c r="S11" t="n">
-        <v>-97000</v>
+        <v>-94000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1626000</v>
+        <v>10940</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>514</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>1930</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>0.41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>11340</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>11340</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>12470</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>10770</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>0.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3481399299500</v>
+        <v>30305603080</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>29750</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>10770</v>
       </c>
       <c r="R12" t="n">
-        <v>-244000</v>
+        <v>8000</v>
       </c>
       <c r="S12" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 요인 및 경영진의 결정에 따른 주가 하락에 대한 불만. 투자자 이탈 우려.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '경영', '주가']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10940</v>
+        <v>18120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="H13" t="n">
-        <v>0.41</v>
+        <v>27.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>11340</v>
+        <v>18860</v>
       </c>
       <c r="K13" t="n">
-        <v>11340</v>
+        <v>18690</v>
       </c>
       <c r="L13" t="n">
-        <v>12470</v>
+        <v>18760</v>
       </c>
       <c r="M13" t="n">
-        <v>10810</v>
+        <v>18100</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>29843283860</v>
+        <v>45041477090</v>
       </c>
       <c r="P13" t="n">
-        <v>29750</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>10810</v>
+        <v>18100</v>
       </c>
       <c r="R13" t="n">
-        <v>8000</v>
+        <v>93000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>삼성중공업 LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['수주 랠리', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>252250</v>
+        <v>251500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.72%</t>
+          <t>'-4.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G14" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="H14" t="n">
         <v>46.35</v>
@@ -1708,13 +1708,13 @@
         <v>262500</v>
       </c>
       <c r="M14" t="n">
-        <v>251500</v>
+        <v>251000</v>
       </c>
       <c r="N14" t="n">
         <v>46.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3086090316250</v>
+        <v>3177467631500</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1723,14 +1723,14 @@
         <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-1433000</v>
+        <v>-1572000</v>
       </c>
       <c r="S14" t="n">
-        <v>-345000</v>
+        <v>-583000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 논란으로 인한 주가 하락에 대한 불만 토로. 외인 및 기관 이탈 우려.</t>
+          <t>정치적 이슈와 맞물려 삼성전자 주가 하락 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '이탈', '주가']</t>
+          <t>['정치 이슈', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18140</v>
+        <v>1613000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>517</v>
       </c>
       <c r="G15" t="n">
-        <v>357</v>
+        <v>1946</v>
       </c>
       <c r="H15" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K15" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L15" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M15" t="n">
-        <v>18100</v>
+        <v>1605000</v>
       </c>
       <c r="N15" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O15" t="n">
-        <v>43734576765</v>
+        <v>3607749492500</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>18100</v>
+        <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>112000</v>
+        <v>-259000</v>
       </c>
       <c r="S15" t="n">
-        <v>33000</v>
+        <v>88000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락, 공매도 증가에 대한 불만. 조선주 순환매 기대.</t>
+          <t>SK하이닉스 주가 하락 및 투자 심리 위축, 정치적 이슈 영향.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '순환매']</t>
+          <t>['주가 하락', '정치 이슈']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G16" t="n">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>27239343940</v>
+        <v>27651261205</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1907,23 +1907,23 @@
         <v>7700</v>
       </c>
       <c r="R16" t="n">
-        <v>-1111000</v>
+        <v>-1233000</v>
       </c>
       <c r="S16" t="n">
-        <v>-30000</v>
+        <v>12000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>기업 가치 저평가 및 실적 악화에 대한 불안감 표출. 유상증자 및 상폐 가능성 언급.</t>
+          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['기업가치', '유상증자', '실적']</t>
+          <t>['실적 부진', '기업 가치 하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15960</v>
+        <v>15880</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.95%</t>
+          <t>'-6.42%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>77006593610</v>
+        <v>77847274975</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -1999,7 +1999,7 @@
         <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>65000</v>
+        <v>68000</v>
       </c>
       <c r="S17" t="n">
         <v>-56000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.47%</t>
+          <t>'-7.83%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>57761104525</v>
+        <v>58863549275</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2091,10 +2091,10 @@
         <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-64000</v>
+        <v>-57000</v>
       </c>
       <c r="S18" t="n">
-        <v>-3000</v>
+        <v>-7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3845</v>
+        <v>3815</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-9.95%</t>
+          <t>'-10.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2168,13 +2168,13 @@
         <v>4495</v>
       </c>
       <c r="M19" t="n">
-        <v>3840</v>
+        <v>3785</v>
       </c>
       <c r="N19" t="n">
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>18481797539</v>
+        <v>18694785813</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>
@@ -2183,7 +2183,7 @@
         <v>2810</v>
       </c>
       <c r="R19" t="n">
-        <v>-89000</v>
+        <v>-91000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261012_14.xlsx
+++ b/data/trending_integrated_20261012_14.xlsx
@@ -581,10 +581,10 @@
         <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19964303180</v>
+        <v>19970008620</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132103845020</v>
+        <v>132153615740</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13730</v>
+        <v>13680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+23.25%</t>
+          <t>'+22.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F4" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>176341980630</v>
+        <v>178012850440</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설 주가 상승 기대감 속 외인 매도세 관찰.</t>
+          <t>금호건설, 금호전기 상장 후 주가 흐름 주목. 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주가 상승', '외인 매도']</t>
+          <t>['금호전기', '외인 매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1595</v>
+        <v>1616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.00%</t>
+          <t>'+16.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11431505728</v>
+        <v>11524740739</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7580</v>
+        <v>7530</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.06%</t>
+          <t>'+6.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F6" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>120469328175</v>
+        <v>121466846980</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼표시멘트 건설 기초 소재 사업 성장 기대 및 투신 매수세 유입.</t>
+          <t>삼표시멘트, 성수메가프로젝트 및 건설기초소재 관련 언급. 공매도 및 국토부 승인 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설 기초 소재', '투신 매수']</t>
+          <t>['성수메가프로젝트', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14080</v>
+        <v>13970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F7" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G7" t="n">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>153679679195</v>
+        <v>154753073765</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>덕산넵코어스 주가 변동성 심화 및 투자 심리 위축, 매도 압력 관찰.</t>
+          <t>덕산넵코어스, 미국 방산주 팔란티어 상승 언급. 대차 공매 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 변동성', '매도 압력']</t>
+          <t>['팔란티어', '대차 공매']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3735</v>
+        <v>3745</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
         <v>122</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>71937409953</v>
+        <v>72292859098</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44950</v>
+        <v>44750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.53%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F9" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G9" t="n">
-        <v>2827</v>
+        <v>2883</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>37254598675</v>
+        <v>37603563750</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB 간암 치료제 FDA 재승인 서류 제출 완료, 상한가 기대감 고조.</t>
+          <t>HLB, 리보세라닙 FDA 재승인 서류 제출 공시. 간암 1차 치료제 관련 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 재승인', '리보세라닙', '공시']</t>
+          <t>['FDA', '리보세라닙', '공시']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2260</v>
+        <v>2245</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
@@ -1346,7 +1346,7 @@
         <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>31743824559</v>
+        <v>31972330689</v>
       </c>
       <c r="P10" t="n">
         <v>2465</v>
@@ -1391,215 +1391,215 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16090</v>
+        <v>10950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>791</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>11340</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>11340</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>12470</v>
       </c>
       <c r="M11" t="n">
-        <v>16050</v>
+        <v>10770</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="O11" t="n">
-        <v>55828522425</v>
+        <v>30404252840</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>29750</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>10770</v>
       </c>
       <c r="R11" t="n">
-        <v>624000</v>
+        <v>8000</v>
       </c>
       <c r="S11" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대차 거래 및 공매도에 대한 의혹 제기. 주가 하락 요인으로 지목하며 반발.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차', '공매도', '주가']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10940</v>
+        <v>16090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>104</v>
+        <v>815</v>
       </c>
       <c r="H12" t="n">
-        <v>0.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11340</v>
+        <v>16670</v>
       </c>
       <c r="K12" t="n">
-        <v>11340</v>
+        <v>16500</v>
       </c>
       <c r="L12" t="n">
-        <v>12470</v>
+        <v>16870</v>
       </c>
       <c r="M12" t="n">
-        <v>10770</v>
+        <v>16050</v>
       </c>
       <c r="N12" t="n">
-        <v>0.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>30305603080</v>
+        <v>56988094450</v>
       </c>
       <c r="P12" t="n">
-        <v>29750</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>10770</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>8000</v>
+        <v>624000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>대우건설, 뱅크런, 대차 해지 관련 언급. 기관 및 외인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['뱅크런', '대차 해지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18120</v>
+        <v>1616000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-3.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>518</v>
       </c>
       <c r="G13" t="n">
-        <v>364</v>
+        <v>1968</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>45041477090</v>
+        <v>3674241252000</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>93000</v>
+        <v>-259000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>88000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성중공업 LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 공매도 우려.</t>
+          <t>SK하이닉스, 현 정부 및 정치인 관련 부정적 발언 다수. 주가 하락 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주 랠리', '주가 하락', '공매도']</t>
+          <t>['정치', '주가 폭망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>251500</v>
+        <v>18120</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="F14" t="n">
-        <v>524</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="H14" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>262000</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>260000</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>262500</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>251000</v>
+        <v>18100</v>
       </c>
       <c r="N14" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3177467631500</v>
+        <v>46662584660</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>18100</v>
       </c>
       <c r="R14" t="n">
-        <v>-1572000</v>
+        <v>93000</v>
       </c>
       <c r="S14" t="n">
-        <v>-583000</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 삼성전자 주가 하락 및 투자 심리 위축.</t>
+          <t>삼성중공업 LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치 이슈', '주가 하락']</t>
+          <t>['수주 랠리', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1613000</v>
+        <v>250750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-4.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="G15" t="n">
-        <v>1946</v>
+        <v>1996</v>
       </c>
       <c r="H15" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K15" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L15" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M15" t="n">
-        <v>1605000</v>
+        <v>250500</v>
       </c>
       <c r="N15" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O15" t="n">
-        <v>3607749492500</v>
+        <v>3286788959000</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R15" t="n">
-        <v>-259000</v>
+        <v>-1572000</v>
       </c>
       <c r="S15" t="n">
-        <v>88000</v>
+        <v>-583000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 하락 및 투자 심리 위축, 정치적 이슈 영향.</t>
+          <t>삼성전자, 현 정권 및 이재명 관련 부정적 언급 다수. 코스피 하락 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치 이슈']</t>
+          <t>['정치', '코스피']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7810</v>
+        <v>7770</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-4.78%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>202</v>
       </c>
       <c r="F16" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>27651261205</v>
+        <v>28339706125</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15880</v>
+        <v>15860</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.42%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>77847274975</v>
+        <v>78387480825</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25900</v>
+        <v>25850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.83%</t>
+          <t>'-8.01%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>58863549275</v>
+        <v>59406508875</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3815</v>
+        <v>3795</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.66%</t>
+          <t>'-11.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H19" t="n">
         <v>1.52</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>18694785813</v>
+        <v>18771323413</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_14.xlsx
+++ b/data/trending_integrated_20261012_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19970008620</v>
+        <v>19973490020</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132153615740</v>
+        <v>132220301420</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13680</v>
+        <v>13570</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+22.80%</t>
+          <t>'+21.81%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F4" t="n">
         <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>178012850440</v>
+        <v>180293832810</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설, 금호전기 상장 후 주가 흐름 주목. 외인 매도세 관찰.</t>
+          <t>전라도 지역 기반의 건설 기대감과 외국인 매도세 속에서 상승 패턴 지속 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['금호전기', '외인 매도']</t>
+          <t>['금호건설', '호남', '외인매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1616</v>
+        <v>1596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.51%</t>
+          <t>'+15.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11524740739</v>
+        <v>11562388967</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7530</v>
+        <v>7500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.36%</t>
+          <t>'+5.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>121466846980</v>
+        <v>122526658895</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13970</v>
+        <v>14100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+1.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F7" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G7" t="n">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>154753073765</v>
+        <v>155786746260</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3745</v>
+        <v>3725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
         <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>72292859098</v>
+        <v>72703703723</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44750</v>
+        <v>44650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F9" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G9" t="n">
-        <v>2883</v>
+        <v>2943</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>37603563750</v>
+        <v>38031880875</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB, 리보세라닙 FDA 재승인 서류 제출 공시. 간암 1차 치료제 관련 기대감.</t>
+          <t>FDA에 리보세라닙 간암 1차 치료제 재승인 서류 제출 완료, 연말 주가 30만 기대감 고조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '공시']</t>
+          <t>['HLB', 'FDA', '재신청', '리보세라닙']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2245</v>
+        <v>2250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
@@ -1346,7 +1346,7 @@
         <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>31972330689</v>
+        <v>32164283716</v>
       </c>
       <c r="P10" t="n">
         <v>2465</v>
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10950</v>
+        <v>16010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>191</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>831</v>
       </c>
       <c r="H11" t="n">
-        <v>0.41</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11340</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>11340</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>12470</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>10770</v>
+        <v>16000</v>
       </c>
       <c r="N11" t="n">
-        <v>0.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>30404252840</v>
+        <v>58850342280</v>
       </c>
       <c r="P11" t="n">
-        <v>29750</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>10770</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>8000</v>
+        <v>624000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>대우건설, 뱅크런, 대차 해지 관련 언급. 기관 및 외인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['뱅크런', '대차 해지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16090</v>
+        <v>1611000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>180</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>512</v>
       </c>
       <c r="G12" t="n">
-        <v>815</v>
+        <v>2061</v>
       </c>
       <c r="H12" t="n">
-        <v>9.470000000000001</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16670</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>16500</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>16870</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>16050</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>9.460000000000001</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>56988094450</v>
+        <v>3794434880500</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>624000</v>
+        <v>-259000</v>
       </c>
       <c r="S12" t="n">
-        <v>-94000</v>
+        <v>88000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대우건설, 뱅크런, 대차 해지 관련 언급. 기관 및 외인 매매 동향 주시.</t>
+          <t>세계 최고 수준의 영업이익에도 불구하고 주가 폭락, 증권사 목표가 하향 및 정치적 요인 의심.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['뱅크런', '대차 해지']</t>
+          <t>['SK하이닉스', '영업이익', '정치', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1616000</v>
+        <v>18060</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.87%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
-        <v>518</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>1968</v>
+        <v>382</v>
       </c>
       <c r="H13" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K13" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L13" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M13" t="n">
-        <v>1605000</v>
+        <v>18050</v>
       </c>
       <c r="N13" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3674241252000</v>
+        <v>50521412640</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>18050</v>
       </c>
       <c r="R13" t="n">
-        <v>-259000</v>
+        <v>93000</v>
       </c>
       <c r="S13" t="n">
-        <v>88000</v>
+        <v>23000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스, 현 정부 및 정치인 관련 부정적 발언 다수. 주가 하락 관련 언급.</t>
+          <t>역대 최대 실적에도 불구하고 주가 하락, LNG·FLNG 수주 랠리 뉴스에도 공매도 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '주가 폭망']</t>
+          <t>['삼성중공업', '실적', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18120</v>
+        <v>250250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.92%</t>
+          <t>'-4.48%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>130</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>538</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>2107</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61</v>
+        <v>46.35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18860</v>
+        <v>262000</v>
       </c>
       <c r="K14" t="n">
-        <v>18690</v>
+        <v>260000</v>
       </c>
       <c r="L14" t="n">
-        <v>18760</v>
+        <v>262500</v>
       </c>
       <c r="M14" t="n">
-        <v>18100</v>
+        <v>250000</v>
       </c>
       <c r="N14" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="O14" t="n">
-        <v>46662584660</v>
+        <v>3394386184500</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>18100</v>
+        <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>93000</v>
+        <v>-1572000</v>
       </c>
       <c r="S14" t="n">
-        <v>23000</v>
+        <v>-583000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성중공업 LNG·FLNG 수주 랠리에도 불구하고 주가 하락 및 공매도 우려.</t>
+          <t>정치적 이슈와 맞물린 증시 전반의 신뢰도 하락 및 외국인/기관 이탈 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['수주 랠리', '주가 하락', '공매도']</t>
+          <t>['정치', '외인기관', '신뢰도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>250750</v>
+        <v>10810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-4.67%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>527</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>1996</v>
+        <v>105</v>
       </c>
       <c r="H15" t="n">
-        <v>46.35</v>
+        <v>0.41</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>262000</v>
+        <v>11340</v>
       </c>
       <c r="K15" t="n">
-        <v>260000</v>
+        <v>11340</v>
       </c>
       <c r="L15" t="n">
-        <v>262500</v>
+        <v>12470</v>
       </c>
       <c r="M15" t="n">
-        <v>250500</v>
+        <v>10770</v>
       </c>
       <c r="N15" t="n">
-        <v>46.38</v>
+        <v>0.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3286788959000</v>
+        <v>30603145085</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>29750</v>
       </c>
       <c r="Q15" t="n">
-        <v>90200</v>
+        <v>10770</v>
       </c>
       <c r="R15" t="n">
-        <v>-1572000</v>
+        <v>8000</v>
       </c>
       <c r="S15" t="n">
-        <v>-583000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자, 현 정권 및 이재명 관련 부정적 언급 다수. 코스피 하락 관련 언급.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,20 +1831,20 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '코스피']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7770</v>
+        <v>7760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-4.90%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F16" t="n">
         <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="H16" t="n">
         <v>26.37</v>
@@ -1898,7 +1898,7 @@
         <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>28339706125</v>
+        <v>28809253340</v>
       </c>
       <c r="P16" t="n">
         <v>17950</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15860</v>
+        <v>15800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="n">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="H17" t="n">
         <v>3.37</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>78387480825</v>
+        <v>79513359310</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25850</v>
+        <v>25700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.01%</t>
+          <t>'-8.54%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2076,13 +2076,13 @@
         <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>25850</v>
+        <v>25700</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>59406508875</v>
+        <v>61281187075</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3795</v>
+        <v>3770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.12%</t>
+          <t>'-11.71%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
         <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" t="n">
         <v>1.52</v>
@@ -2168,13 +2168,13 @@
         <v>4495</v>
       </c>
       <c r="M19" t="n">
-        <v>3785</v>
+        <v>3735</v>
       </c>
       <c r="N19" t="n">
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>18771323413</v>
+        <v>19078117803</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_14.xlsx
+++ b/data/trending_integrated_20261012_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19973490020</v>
+        <v>19975693780</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,7 +670,7 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132220301420</v>
+        <v>132292367120</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13570</v>
+        <v>13615</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.81%</t>
+          <t>'+22.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
         <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>180293832810</v>
+        <v>181943971840</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전라도 지역 기반의 건설 기대감과 외국인 매도세 속에서 상승 패턴 지속 전망.</t>
+          <t>상승 가능성에 대한 기대감 표출. 다만, 의도적인 상승 억제 및 외인 대량 매도 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['금호건설', '호남', '외인매도']</t>
+          <t>['상승', '외인', '개미']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.07%</t>
+          <t>'+15.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11562388967</v>
+        <v>11648306926</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7500</v>
+        <v>7580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.93%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F6" t="n">
         <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>122526658895</v>
+        <v>124310744695</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14100</v>
+        <v>13960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.37%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="H7" t="n">
         <v>0.21</v>
@@ -1070,7 +1070,7 @@
         <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>155786746260</v>
+        <v>156714248850</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 미국 방산주 팔란티어 상승 언급. 대차 공매 및 주가 하락 우려.</t>
+          <t>주가 상승 후 급락에 대한 실망감. 대차 공매도 세력의 움직임 경계.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['팔란티어', '대차 공매']</t>
+          <t>['대차', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3725</v>
+        <v>3745</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>72703703723</v>
+        <v>72893625848</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44650</v>
+        <v>2270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.19%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="F9" t="n">
-        <v>256</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>2943</v>
+        <v>143</v>
       </c>
       <c r="H9" t="n">
-        <v>13.33</v>
+        <v>1.48</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45650</v>
+        <v>2305</v>
       </c>
       <c r="K9" t="n">
-        <v>47550</v>
+        <v>2430</v>
       </c>
       <c r="L9" t="n">
-        <v>47550</v>
+        <v>2445</v>
       </c>
       <c r="M9" t="n">
-        <v>43900</v>
+        <v>2210</v>
       </c>
       <c r="N9" t="n">
-        <v>13.39</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
-        <v>38031880875</v>
+        <v>32352253670</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>2465</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>865</v>
       </c>
       <c r="R9" t="n">
-        <v>-153000</v>
+        <v>-497000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA에 리보세라닙 간암 1차 치료제 재승인 서류 제출 완료, 연말 주가 30만 기대감 고조.</t>
+          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HLB', 'FDA', '재신청', '리보세라닙']</t>
+          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2250</v>
+        <v>44725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>255</v>
       </c>
       <c r="G10" t="n">
-        <v>142</v>
+        <v>3028</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>13.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2305</v>
+        <v>45650</v>
       </c>
       <c r="K10" t="n">
-        <v>2430</v>
+        <v>47550</v>
       </c>
       <c r="L10" t="n">
-        <v>2445</v>
+        <v>47550</v>
       </c>
       <c r="M10" t="n">
-        <v>2210</v>
+        <v>43900</v>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>13.39</v>
       </c>
       <c r="O10" t="n">
-        <v>32164283716</v>
+        <v>38696298175</v>
       </c>
       <c r="P10" t="n">
-        <v>2465</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>865</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-497000</v>
+        <v>-153000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
+          <t>FDA 리보세라닙 재승인 서류 제출 공시. 긍정적인 뉴스에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
+          <t>['FDA', '리보세라닙', '공시']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16010</v>
+        <v>16050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.96%</t>
+          <t>'-3.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="H11" t="n">
         <v>9.470000000000001</v>
@@ -1432,13 +1432,13 @@
         <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>16000</v>
+        <v>15950</v>
       </c>
       <c r="N11" t="n">
         <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>58850342280</v>
+        <v>61842521925</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>대우건설, 뱅크런, 대차 해지 관련 언급. 기관 및 외인 매매 동향 주시.</t>
+          <t>계속되는 주가 하락에 대한 불만과 특정 세력(모간이, 대차 해지 세력)에 대한 비난.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['뱅크런', '대차 해지']</t>
+          <t>['대차', '주가', '뱅크런']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1611000</v>
+        <v>252000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="G12" t="n">
-        <v>2061</v>
+        <v>2010</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>249500</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>3794434880500</v>
+        <v>3633225586750</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-259000</v>
+        <v>-1572000</v>
       </c>
       <c r="S12" t="n">
-        <v>88000</v>
+        <v>-583000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>세계 최고 수준의 영업이익에도 불구하고 주가 폭락, 증권사 목표가 하향 및 정치적 요인 의심.</t>
+          <t>정치적 이슈와 연결된 부정적 시장 전망. 외인·기관 신뢰도 하락 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '영업이익', '정치', '주가조작']</t>
+          <t>['코스피', '외인', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18060</v>
+        <v>1614000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.24%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>133</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>509</v>
       </c>
       <c r="G13" t="n">
-        <v>382</v>
+        <v>1962</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>18050</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>50521412640</v>
+        <v>3915789406500</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>18050</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>93000</v>
+        <v>-259000</v>
       </c>
       <c r="S13" t="n">
-        <v>23000</v>
+        <v>88000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>역대 최대 실적에도 불구하고 주가 하락, LNG·FLNG 수주 랠리 뉴스에도 공매도 우려.</t>
+          <t>세계적인 실적에도 불구하고 주가 폭락에 대한 강한 불만. 정치적 요인과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['삼성중공업', '실적', '수주', '공매도']</t>
+          <t>['주가', '실적', '정치']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>250250</v>
+        <v>18060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.48%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>138</v>
       </c>
       <c r="F14" t="n">
-        <v>538</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>2107</v>
+        <v>402</v>
       </c>
       <c r="H14" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>262000</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>260000</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>262500</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>250000</v>
+        <v>17970</v>
       </c>
       <c r="N14" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>3394386184500</v>
+        <v>55906838790</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>17970</v>
       </c>
       <c r="R14" t="n">
-        <v>-1572000</v>
+        <v>93000</v>
       </c>
       <c r="S14" t="n">
-        <v>-583000</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물린 증시 전반의 신뢰도 하락 및 외국인/기관 이탈 우려.</t>
+          <t>실적 호조에도 불구하고 주가 하락에 대한 불만. 정치적 요인과 공매도 문제 지적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '외인기관', '신뢰도']</t>
+          <t>['실적', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,191 +1752,191 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10810</v>
+        <v>7790</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.67%</t>
+          <t>'-4.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
-        <v>105</v>
+        <v>814</v>
       </c>
       <c r="H15" t="n">
-        <v>0.41</v>
+        <v>26.37</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11340</v>
+        <v>8160</v>
       </c>
       <c r="K15" t="n">
-        <v>11340</v>
+        <v>8070</v>
       </c>
       <c r="L15" t="n">
-        <v>12470</v>
+        <v>8110</v>
       </c>
       <c r="M15" t="n">
-        <v>10770</v>
+        <v>7700</v>
       </c>
       <c r="N15" t="n">
-        <v>0.44</v>
+        <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>30603145085</v>
+        <v>29570066715</v>
       </c>
       <c r="P15" t="n">
-        <v>29750</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>10770</v>
+        <v>7700</v>
       </c>
       <c r="R15" t="n">
-        <v>8000</v>
+        <v>-1233000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['실적 부진', '기업 가치 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7760</v>
+        <v>10670</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.90%</t>
+          <t>'-5.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>203</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>811</v>
+        <v>108</v>
       </c>
       <c r="H16" t="n">
-        <v>26.37</v>
+        <v>0.41</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8160</v>
+        <v>11340</v>
       </c>
       <c r="K16" t="n">
-        <v>8070</v>
+        <v>11340</v>
       </c>
       <c r="L16" t="n">
-        <v>8110</v>
+        <v>12470</v>
       </c>
       <c r="M16" t="n">
-        <v>7700</v>
+        <v>10550</v>
       </c>
       <c r="N16" t="n">
-        <v>26.38</v>
+        <v>0.44</v>
       </c>
       <c r="O16" t="n">
-        <v>28809253340</v>
+        <v>31110410450</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>29750</v>
       </c>
       <c r="Q16" t="n">
-        <v>7700</v>
+        <v>10550</v>
       </c>
       <c r="R16" t="n">
-        <v>-1233000</v>
+        <v>8000</v>
       </c>
       <c r="S16" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적 부진', '기업 가치 하락']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15800</v>
+        <v>15820</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.89%</t>
+          <t>'-6.78%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
         <v>537</v>
@@ -1990,7 +1990,7 @@
         <v>3.97</v>
       </c>
       <c r="O17" t="n">
-        <v>79513359310</v>
+        <v>81128539655</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI, 광통신 테마 언급과 함께 3분기 어닝 서프라이즈 기록. 유튜버의 바람잡이 의혹 및 공매도 규제 논의.</t>
+          <t>3분기 어닝 서프라이즈 발표. 긍정적인 실적 기반으로 한 기대감과 주가 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '실적', '공매도']</t>
+          <t>['실적', '어닝 서프라이즈', '광섬유']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25700</v>
+        <v>25750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.54%</t>
+          <t>'-8.36%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2076,13 +2076,13 @@
         <v>27800</v>
       </c>
       <c r="M18" t="n">
-        <v>25700</v>
+        <v>25600</v>
       </c>
       <c r="N18" t="n">
         <v>10.02</v>
       </c>
       <c r="O18" t="n">
-        <v>61281187075</v>
+        <v>63847948350</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3770</v>
+        <v>3815</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.71%</t>
+          <t>'-10.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
         <v>31</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>19078117803</v>
+        <v>19166065588</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>
